--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,6 +1738,268 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121673149</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56251</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gärdefjärdens naturreservat, Skogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>804849</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7153950</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>RMÖ, Pettersson D500X</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Bäckström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Bäckström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121673142</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56258</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gärdefjärdens naturreservat, Skogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>804849</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7153950</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>RMÖ, Pettersson D500X</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Bäckström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -1740,7 +1740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121673146</v>
+        <v>121673149</v>
       </c>
       <c r="B11" t="n">
         <v>56251</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1876,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121673145</v>
+        <v>121673152</v>
       </c>
       <c r="B12" t="n">
         <v>56258</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,6 +2010,118 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126174063</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79979</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strömmen, Strömmen, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>804745</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7153568</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fabian Stenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>126174063</v>
       </c>
       <c r="B13" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>126174063</v>
       </c>
       <c r="B13" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 63587-2019 artfynd.xlsx
+++ b/artfynd/A 63587-2019 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>126174063</v>
       </c>
       <c r="B13" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
